--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_46.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_46.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5940683.389502842</v>
+        <v>5980620.568277922</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6767152.318645785</v>
+        <v>6767152.318645784</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6767152.318645785</v>
+        <v>6767152.318645784</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2916902.906517475</v>
+        <v>2916902.90651747</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2916902.906517475</v>
+        <v>2916902.90651747</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39093790.23457033</v>
+        <v>39093790.23457034</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +666,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>348.3778604107422</v>
       </c>
       <c r="G2" t="n">
         <v>403.7573722870162</v>
@@ -687,28 +687,28 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>522.1267819420526</v>
+        <v>814</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5855355810472</v>
+        <v>814</v>
       </c>
       <c r="O2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>329.543106465188</v>
       </c>
       <c r="Q2" t="n">
-        <v>797.8013999999999</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>438.3363995050528</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -745,7 +745,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>156.9894696000266</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>57.72562438342279</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -790,10 +790,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>400.2103597601867</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -842,16 +842,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>114.9691617061058</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
       </c>
       <c r="O4" t="n">
-        <v>240.445564079015</v>
+        <v>211.2354862247934</v>
       </c>
       <c r="P4" t="n">
         <v>287.4478973282775</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>481.9993129555745</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -915,19 +915,19 @@
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>814.0000000000001</v>
+        <v>797.8013999999998</v>
       </c>
       <c r="L5" t="n">
-        <v>814.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>507.74003719117</v>
+        <v>814</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>370.9706110579117</v>
+        <v>515.8461179080153</v>
       </c>
       <c r="R5" t="n">
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
         <v>279.2852146029995</v>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>352.4782721065219</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
-        <v>266.3820012865855</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
         <v>5.357765217513816</v>
@@ -1079,10 +1079,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617061044</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>297.3920501269273</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47457824299391</v>
+        <v>392.9628099457241</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1140,13 +1140,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>4.889628708011855</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G8" t="n">
-        <v>347.2456039897459</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -1155,10 +1155,10 @@
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>814.0000000000045</v>
+        <v>313.154501610127</v>
       </c>
       <c r="L8" t="n">
-        <v>700.3237126680116</v>
+        <v>814</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
@@ -1170,10 +1170,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
-        <v>797.801400000018</v>
+        <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1188,16 +1188,16 @@
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>175.4172848236332</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>57.93598414360948</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>114.9691617061022</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>297.3920501269255</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,22 +1368,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>197.0013848176395</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>124.0498976023938</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,13 +1413,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
         <v>424.2212965486107</v>
@@ -1431,7 +1431,7 @@
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>286.3174326828064</v>
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R13" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1602,7 +1602,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>230.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>198.4745782429939</v>
@@ -1611,10 +1611,10 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>67.57968198731129</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>243.8481678023229</v>
+        <v>235.174244430328</v>
       </c>
       <c r="T14" t="n">
         <v>335.6755817285639</v>
@@ -1796,16 +1796,16 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>139.1349830766931</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>92.1326498274306</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -2024,16 +2024,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>282.0711266385952</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2042,13 +2042,13 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>339.4016293563777</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>8.465352849462363</v>
       </c>
     </row>
     <row r="20">
@@ -2094,7 +2094,7 @@
         <v>124.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>128.5790500889954</v>
+        <v>129.0096587035274</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2276,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7929984536983</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2328,10 +2328,10 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>124.3267636724302</v>
+        <v>124.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>129.0096587035274</v>
+        <v>128.5790500890098</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2501,25 +2501,25 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>107.8765809499618</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>338.6387678008247</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>5.732606045363564</v>
       </c>
       <c r="C26" t="n">
-        <v>189.411675845388</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2750,13 +2750,13 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>51.77560670118918</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>183.0096587035274</v>
@@ -2838,13 +2838,13 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>361.6755817285639</v>
       </c>
       <c r="U29" t="n">
-        <v>424.2212965486107</v>
+        <v>20.80957970762738</v>
       </c>
       <c r="V29" t="n">
         <v>404.8510241668239</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>45.1451880859778</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>345.920735428856</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3054,28 +3054,28 @@
         <v>56.12488247690067</v>
       </c>
       <c r="L32" t="n">
-        <v>727.1079320762982</v>
+        <v>727.1079320760407</v>
       </c>
       <c r="M32" t="n">
-        <v>256.9910820920259</v>
+        <v>773.0000000000412</v>
       </c>
       <c r="N32" t="n">
-        <v>773.0000000000412</v>
+        <v>153.5855355810884</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>67.52171792394017</v>
+        <v>170.9272644348829</v>
       </c>
       <c r="Q32" t="n">
         <v>757.61730000004</v>
       </c>
       <c r="R32" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>203.8481678023229</v>
+        <v>212.3047591877378</v>
       </c>
       <c r="T32" t="n">
         <v>295.6755817285639</v>
@@ -3221,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>109.2047614405436</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>70.05053078764654</v>
       </c>
       <c r="Q34" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3288,22 +3288,22 @@
         <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>10.23281455293948</v>
+        <v>351.8156858381437</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
       </c>
       <c r="M35" t="n">
-        <v>598.5739533769843</v>
+        <v>256.9910820920331</v>
       </c>
       <c r="N35" t="n">
         <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>773.0000000000484</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>329.9706110579601</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>108.4418998849671</v>
+        <v>226.7541306595498</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,19 +3516,19 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H38" t="n">
-        <v>117.0096587035274</v>
+        <v>125.4662500889416</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>757.6173000000546</v>
+        <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>697.2557842279629</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320762842</v>
       </c>
       <c r="M38" t="n">
         <v>256.9910820920404</v>
@@ -3537,16 +3537,16 @@
         <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>397.7077537619086</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>377.6514823271291</v>
+        <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
-        <v>8.456591385414804</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3686,25 +3686,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>298.1276103624089</v>
       </c>
       <c r="P40" t="n">
-        <v>70.05053078767355</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>81.41167584538807</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>197.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>0.1827320236524019</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3798,7 +3798,7 @@
         <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
@@ -3893,16 +3893,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>74.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>2.60713178856368</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>67.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>144.7018369625984</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>142.4109888009625</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>197.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>174.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>138.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>145.1680871864211</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>110.3221348330963</v>
+        <v>360.2737972923793</v>
       </c>
       <c r="S45" t="n">
         <v>279.5639999646113</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4175,7 +4175,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>26.62578595604541</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1510.488528253487</v>
+        <v>1453.405934013821</v>
       </c>
       <c r="C2" t="n">
-        <v>1460.514206795918</v>
+        <v>1403.431612556251</v>
       </c>
       <c r="D2" t="n">
-        <v>1450.070615139504</v>
+        <v>1392.988020899837</v>
       </c>
       <c r="E2" t="n">
-        <v>1445.663251900242</v>
+        <v>1388.580657660576</v>
       </c>
       <c r="F2" t="n">
         <v>1036.683828962857</v>
@@ -4330,16 +4330,16 @@
         <v>1578.734058104141</v>
       </c>
       <c r="M2" t="n">
-        <v>1857.193268263684</v>
+        <v>1562.371835881919</v>
       </c>
       <c r="N2" t="n">
-        <v>2466.502222222222</v>
+        <v>1546.009613659696</v>
       </c>
       <c r="O2" t="n">
-        <v>2450.14</v>
+        <v>2351.869613659696</v>
       </c>
       <c r="P2" t="n">
-        <v>3256</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q2" t="n">
         <v>3256</v>
@@ -4348,25 +4348,25 @@
         <v>3256</v>
       </c>
       <c r="S2" t="n">
-        <v>2813.235960095906</v>
+        <v>3160.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>2624.67476643069</v>
+        <v>2567.592172191024</v>
       </c>
       <c r="U2" t="n">
-        <v>2372.936083048255</v>
+        <v>2315.853488808589</v>
       </c>
       <c r="V2" t="n">
-        <v>2140.763331364595</v>
+        <v>2083.680737124928</v>
       </c>
       <c r="W2" t="n">
-        <v>1899.982042494951</v>
+        <v>1842.899448255284</v>
       </c>
       <c r="X2" t="n">
-        <v>1705.757968292256</v>
+        <v>1648.67537405259</v>
       </c>
       <c r="Y2" t="n">
-        <v>1593.316117097502</v>
+        <v>1536.233522857836</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>931.509519579215</v>
+        <v>65.12</v>
       </c>
       <c r="C3" t="n">
-        <v>566.7621332706096</v>
+        <v>65.12</v>
       </c>
       <c r="D3" t="n">
-        <v>566.7621332706096</v>
+        <v>65.12</v>
       </c>
       <c r="E3" t="n">
-        <v>566.7621332706096</v>
+        <v>65.12</v>
       </c>
       <c r="F3" t="n">
-        <v>223.6952218182087</v>
+        <v>65.12</v>
       </c>
       <c r="G3" t="n">
-        <v>223.6952218182087</v>
+        <v>65.12</v>
       </c>
       <c r="H3" t="n">
-        <v>223.6952218182087</v>
+        <v>65.12</v>
       </c>
       <c r="I3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1220.552420368536</v>
+        <v>1162.243708870129</v>
       </c>
       <c r="R3" t="n">
-        <v>1071.791008962092</v>
+        <v>1013.482297463685</v>
       </c>
       <c r="S3" t="n">
-        <v>1004.554645361474</v>
+        <v>946.2459338630675</v>
       </c>
       <c r="T3" t="n">
-        <v>999.1427613033796</v>
+        <v>940.8340498049728</v>
       </c>
       <c r="U3" t="n">
-        <v>998.9302766971304</v>
+        <v>536.5811611583194</v>
       </c>
       <c r="V3" t="n">
-        <v>984.2730371097363</v>
+        <v>117.8835175305213</v>
       </c>
       <c r="W3" t="n">
-        <v>951.5728927563741</v>
+        <v>85.18337317715914</v>
       </c>
       <c r="X3" t="n">
-        <v>931.509519579215</v>
+        <v>65.12</v>
       </c>
       <c r="Y3" t="n">
-        <v>931.509519579215</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="4">
@@ -4455,43 +4455,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>648.7544645575567</v>
+        <v>911.1945562607825</v>
       </c>
       <c r="C4" t="n">
-        <v>774.7564703759925</v>
+        <v>1037.196562079218</v>
       </c>
       <c r="D4" t="n">
-        <v>888.0756145009926</v>
+        <v>1040.461237304043</v>
       </c>
       <c r="E4" t="n">
-        <v>1005.904518712406</v>
+        <v>1158.290141515456</v>
       </c>
       <c r="F4" t="n">
-        <v>1130.265491304341</v>
+        <v>1282.651114107392</v>
       </c>
       <c r="G4" t="n">
-        <v>1283.672057191226</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="H4" t="n">
-        <v>1453.188642350624</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="I4" t="n">
-        <v>1546.422113931144</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="J4" t="n">
-        <v>1546.422113931144</v>
+        <v>1436.057679994277</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931144</v>
+        <v>1546.422113931146</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931144</v>
+        <v>1522.63663094349</v>
       </c>
       <c r="M4" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415662</v>
       </c>
       <c r="N4" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.872300969515</v>
       </c>
       <c r="O4" t="n">
         <v>1014.503122964673</v>
@@ -4521,10 +4521,10 @@
         <v>536.9971268912645</v>
       </c>
       <c r="X4" t="n">
-        <v>536.9971268912645</v>
+        <v>688.027917915458</v>
       </c>
       <c r="Y4" t="n">
-        <v>536.9971268912645</v>
+        <v>799.4372185944903</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6498286273397</v>
+        <v>65.12</v>
       </c>
       <c r="L5" t="n">
-        <v>415.2876064051173</v>
+        <v>870.98</v>
       </c>
       <c r="M5" t="n">
-        <v>920.1465133829104</v>
+        <v>1375.838906977793</v>
       </c>
       <c r="N5" t="n">
-        <v>1213.137788947385</v>
+        <v>1359.476684755571</v>
       </c>
       <c r="O5" t="n">
-        <v>2018.997788947385</v>
+        <v>2165.336684755571</v>
       </c>
       <c r="P5" t="n">
-        <v>2824.857788947385</v>
+        <v>2971.196684755571</v>
       </c>
       <c r="Q5" t="n">
         <v>3256</v>
@@ -4585,25 +4585,25 @@
         <v>3002.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2502.740639767053</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T5" t="n">
-        <v>2220.634362390286</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U5" t="n">
-        <v>1968.895679007851</v>
+        <v>2372.936083048255</v>
       </c>
       <c r="V5" t="n">
-        <v>1736.722927324191</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W5" t="n">
-        <v>1495.941638454547</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X5" t="n">
-        <v>1301.717564251852</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y5" t="n">
-        <v>1189.275713057098</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>729.6731546075238</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="C6" t="n">
-        <v>729.6731546075238</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="D6" t="n">
-        <v>729.6731546075238</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="E6" t="n">
-        <v>729.6731546075238</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="F6" t="n">
-        <v>729.6731546075238</v>
+        <v>400.6433203903244</v>
       </c>
       <c r="G6" t="n">
         <v>400.6433203903244</v>
@@ -4658,31 +4658,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1220.552420368536</v>
+        <v>1045.724879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1071.791008962092</v>
+        <v>896.9634684666578</v>
       </c>
       <c r="S6" t="n">
-        <v>802.7182803897832</v>
+        <v>829.7271048660403</v>
       </c>
       <c r="T6" t="n">
-        <v>797.3063963316885</v>
+        <v>824.3152208079456</v>
       </c>
       <c r="U6" t="n">
-        <v>797.0939117254392</v>
+        <v>824.1027362016963</v>
       </c>
       <c r="V6" t="n">
-        <v>782.4366721380451</v>
+        <v>809.4454966143022</v>
       </c>
       <c r="W6" t="n">
-        <v>749.7365277846829</v>
+        <v>776.7453522609401</v>
       </c>
       <c r="X6" t="n">
-        <v>729.6731546075238</v>
+        <v>756.6819790837809</v>
       </c>
       <c r="Y6" t="n">
-        <v>729.6731546075238</v>
+        <v>756.6819790837809</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>410.4906232651248</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="C7" t="n">
-        <v>536.4926290835606</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="D7" t="n">
-        <v>649.8117732085607</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="E7" t="n">
-        <v>767.6406774199737</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="F7" t="n">
-        <v>892.0016500119092</v>
+        <v>860.1794923691459</v>
       </c>
       <c r="G7" t="n">
-        <v>1045.408215898794</v>
+        <v>1013.586058256031</v>
       </c>
       <c r="H7" t="n">
-        <v>1214.924801058192</v>
+        <v>1183.102643415429</v>
       </c>
       <c r="I7" t="n">
-        <v>1436.057679994275</v>
+        <v>1404.235522351512</v>
       </c>
       <c r="J7" t="n">
-        <v>1436.057679994275</v>
+        <v>1436.057679994274</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931143</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="L7" t="n">
-        <v>1522.636630943488</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="M7" t="n">
-        <v>1400.786518415659</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1227.872300969513</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O7" t="n">
-        <v>984.9979938189928</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P7" t="n">
-        <v>694.6465823762883</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>365.5160102292195</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R7" t="n">
         <v>65.12</v>
@@ -4749,19 +4749,19 @@
         <v>290.445934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>290.445934252978</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V7" t="n">
-        <v>290.445934252978</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="W7" t="n">
-        <v>290.445934252978</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="X7" t="n">
-        <v>290.445934252978</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="Y7" t="n">
-        <v>298.7332855988327</v>
+        <v>735.8185197772104</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>645.3251259330123</v>
+        <v>1857.446338054225</v>
       </c>
       <c r="C8" t="n">
-        <v>595.3508044754426</v>
+        <v>1460.514206795918</v>
       </c>
       <c r="D8" t="n">
-        <v>584.9072128190287</v>
+        <v>1450.070615139504</v>
       </c>
       <c r="E8" t="n">
-        <v>580.4998495797674</v>
+        <v>1445.663251900242</v>
       </c>
       <c r="F8" t="n">
-        <v>575.5608306827858</v>
+        <v>1036.683828962857</v>
       </c>
       <c r="G8" t="n">
-        <v>224.8076953396081</v>
+        <v>628.8480993800122</v>
       </c>
       <c r="H8" t="n">
         <v>216.7171309926107</v>
@@ -4798,22 +4798,22 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>431.6498286273351</v>
+        <v>937.5543724554943</v>
       </c>
       <c r="L8" t="n">
-        <v>530.112139063687</v>
+        <v>921.1921502332721</v>
       </c>
       <c r="M8" t="n">
-        <v>1034.97104604148</v>
+        <v>1426.051057211065</v>
       </c>
       <c r="N8" t="n">
-        <v>1644.280000000018</v>
+        <v>2035.360011169603</v>
       </c>
       <c r="O8" t="n">
-        <v>2450.140000000018</v>
+        <v>2841.220011169603</v>
       </c>
       <c r="P8" t="n">
-        <v>3256.000000000018</v>
+        <v>2824.857788947385</v>
       </c>
       <c r="Q8" t="n">
         <v>3256</v>
@@ -4831,16 +4831,16 @@
         <v>2719.893892848992</v>
       </c>
       <c r="V8" t="n">
-        <v>2083.680737124928</v>
+        <v>2487.721141165332</v>
       </c>
       <c r="W8" t="n">
-        <v>1842.899448255284</v>
+        <v>2246.939852295688</v>
       </c>
       <c r="X8" t="n">
-        <v>1244.634970012185</v>
+        <v>2052.715778092993</v>
       </c>
       <c r="Y8" t="n">
-        <v>728.152714777027</v>
+        <v>1940.273926898239</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>65.12</v>
+        <v>754.3203429896864</v>
       </c>
       <c r="E9" t="n">
-        <v>65.12</v>
+        <v>408.1869114524009</v>
       </c>
       <c r="F9" t="n">
         <v>65.12</v>
@@ -4907,19 +4907,19 @@
         <v>999.1427613033796</v>
       </c>
       <c r="U9" t="n">
-        <v>940.6215651987236</v>
+        <v>998.9302766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>521.9239215709254</v>
+        <v>984.2730371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>85.18337317715914</v>
+        <v>951.5728927563741</v>
       </c>
       <c r="X9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>65.12</v>
+        <v>931.509519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>402.2032719192701</v>
+        <v>1189.272059776293</v>
       </c>
       <c r="C10" t="n">
-        <v>528.2052777377058</v>
+        <v>1315.274065594728</v>
       </c>
       <c r="D10" t="n">
-        <v>641.5244218627059</v>
+        <v>1428.593209719729</v>
       </c>
       <c r="E10" t="n">
-        <v>759.353326074119</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="F10" t="n">
-        <v>883.7142986660544</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="G10" t="n">
-        <v>1037.12086455294</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="H10" t="n">
-        <v>1206.637449712337</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="I10" t="n">
-        <v>1427.77032864842</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994272</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.42211393114</v>
+        <v>1546.422113931141</v>
       </c>
       <c r="L10" t="n">
-        <v>1546.42211393114</v>
+        <v>1522.636630943486</v>
       </c>
       <c r="M10" t="n">
-        <v>1430.29164756134</v>
+        <v>1400.786518415658</v>
       </c>
       <c r="N10" t="n">
-        <v>1257.377430115193</v>
+        <v>1227.872300969511</v>
       </c>
       <c r="O10" t="n">
-        <v>1014.503122964673</v>
+        <v>984.9979938189909</v>
       </c>
       <c r="P10" t="n">
-        <v>724.1517115219688</v>
+        <v>694.6465823762865</v>
       </c>
       <c r="Q10" t="n">
-        <v>395.0211393749001</v>
+        <v>365.5160102292177</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
       </c>
       <c r="S10" t="n">
-        <v>102.3702550941731</v>
+        <v>65.12</v>
       </c>
       <c r="T10" t="n">
-        <v>290.445934252978</v>
+        <v>197.8111266228648</v>
       </c>
       <c r="U10" t="n">
-        <v>290.445934252978</v>
+        <v>444.3623192611515</v>
       </c>
       <c r="V10" t="n">
-        <v>290.445934252978</v>
+        <v>643.1837121470974</v>
       </c>
       <c r="W10" t="n">
-        <v>290.445934252978</v>
+        <v>815.0746304067748</v>
       </c>
       <c r="X10" t="n">
-        <v>290.445934252978</v>
+        <v>966.1054214309682</v>
       </c>
       <c r="Y10" t="n">
-        <v>290.445934252978</v>
+        <v>1077.514722110001</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1179.625545316074</v>
+        <v>417.1649250963513</v>
       </c>
       <c r="C11" t="n">
-        <v>980.6342475204788</v>
+        <v>190.4229268711049</v>
       </c>
       <c r="D11" t="n">
-        <v>793.4229790963881</v>
+        <v>65.12</v>
       </c>
       <c r="E11" t="n">
-        <v>612.24793908945</v>
+        <v>65.12</v>
       </c>
       <c r="F11" t="n">
-        <v>430.5412434247916</v>
+        <v>65.12</v>
       </c>
       <c r="G11" t="n">
-        <v>249.9782411146742</v>
+        <v>65.12</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5038,13 +5038,13 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1693.331756443634</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2204.180585172569</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>2817.400904947332</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="O11" t="n">
         <v>2817.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3256</v>
       </c>
       <c r="R11" t="n">
-        <v>3256</v>
+        <v>3229.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>2983.426093128967</v>
+        <v>2957.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2983.426093128967</v>
+        <v>2591.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2554.919732978855</v>
+        <v>2163.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>2145.979304527517</v>
+        <v>1754.510435278166</v>
       </c>
       <c r="W11" t="n">
-        <v>1728.430338890196</v>
+        <v>1336.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1728.430338890196</v>
+        <v>965.9697186704734</v>
       </c>
       <c r="Y11" t="n">
-        <v>1439.220810927766</v>
+        <v>676.7601907080427</v>
       </c>
     </row>
     <row r="12">
@@ -5111,13 +5111,13 @@
         <v>72.91487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>419.6213981428639</v>
+        <v>215.7971006891144</v>
       </c>
       <c r="K12" t="n">
-        <v>831.5642142372474</v>
+        <v>627.7399167834978</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
         <v>1430.670920121557</v>
@@ -5211,7 +5211,7 @@
         <v>409.3389893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>409.3389893823512</v>
+        <v>65.12</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5245,16 +5245,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>653.4059340138207</v>
+        <v>895.5001121224765</v>
       </c>
       <c r="C14" t="n">
-        <v>452.9265620512006</v>
+        <v>695.0207401598564</v>
       </c>
       <c r="D14" t="n">
-        <v>291.9779198897361</v>
+        <v>534.0720979983919</v>
       </c>
       <c r="E14" t="n">
-        <v>223.7156148520479</v>
+        <v>379.1596842540801</v>
       </c>
       <c r="F14" t="n">
         <v>223.7156148520479</v>
@@ -5278,7 +5278,7 @@
         <v>1971.995479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2482.844308114459</v>
+        <v>2204.180585172569</v>
       </c>
       <c r="N14" t="n">
         <v>2817.400904947332</v>
@@ -5296,25 +5296,25 @@
         <v>3256</v>
       </c>
       <c r="S14" t="n">
-        <v>3009.688719391593</v>
+        <v>3018.450258151184</v>
       </c>
       <c r="T14" t="n">
-        <v>2670.622475221327</v>
+        <v>2679.384013980917</v>
       </c>
       <c r="U14" t="n">
-        <v>2268.378741333841</v>
+        <v>2277.140280093432</v>
       </c>
       <c r="V14" t="n">
-        <v>1885.70093914513</v>
+        <v>1894.462477904721</v>
       </c>
       <c r="W14" t="n">
-        <v>1494.414599770435</v>
+        <v>1503.176138530026</v>
       </c>
       <c r="X14" t="n">
-        <v>1149.68547506269</v>
+        <v>1158.447013822281</v>
       </c>
       <c r="Y14" t="n">
-        <v>886.7385733628859</v>
+        <v>895.5001121224765</v>
       </c>
     </row>
     <row r="15">
@@ -5351,7 +5351,7 @@
         <v>222.6113981428639</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8042142372473</v>
+        <v>576.3405228441038</v>
       </c>
       <c r="L15" t="n">
         <v>847.690984439304</v>
@@ -5363,7 +5363,7 @@
         <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
-        <v>2051.564262473451</v>
+        <v>1803.074262473451</v>
       </c>
       <c r="P15" t="n">
         <v>2164.093606942957</v>
@@ -5439,13 +5439,13 @@
         <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>458.4993576555707</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>65.12</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>65.12</v>
+        <v>158.1832826539703</v>
       </c>
       <c r="Q16" t="n">
         <v>65.12</v>
@@ -5509,22 +5509,22 @@
         <v>456.4291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>887.4717564436343</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>887.4717564436343</v>
+        <v>1971.995479385524</v>
       </c>
       <c r="M17" t="n">
-        <v>1398.320585172569</v>
+        <v>2482.844308114459</v>
       </c>
       <c r="N17" t="n">
-        <v>2011.540904947332</v>
+        <v>3096.064627889222</v>
       </c>
       <c r="O17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="P17" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q17" t="n">
         <v>3256</v>
@@ -5582,28 +5582,28 @@
         <v>65.12</v>
       </c>
       <c r="I18" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J18" t="n">
-        <v>404.4452825072959</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>593.6380986016793</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>864.9885601968795</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>1227.279101939739</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N18" t="n">
-        <v>1360.559386547307</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1599.601838231026</v>
+        <v>1384.233075899029</v>
       </c>
       <c r="P18" t="n">
-        <v>1712.131182700533</v>
+        <v>1772.972420368536</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5640,55 +5640,55 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>422.5399739669084</v>
+        <v>405.793354586564</v>
       </c>
       <c r="C19" t="n">
-        <v>428.7519797853442</v>
+        <v>412.0053604049997</v>
       </c>
       <c r="D19" t="n">
-        <v>428.7519797853442</v>
+        <v>405.4031199448427</v>
       </c>
       <c r="E19" t="n">
-        <v>428.7519797853442</v>
+        <v>403.4022059681189</v>
       </c>
       <c r="F19" t="n">
-        <v>433.3229523772797</v>
+        <v>407.9731785600544</v>
       </c>
       <c r="G19" t="n">
-        <v>466.939518264165</v>
+        <v>441.5897444469397</v>
       </c>
       <c r="H19" t="n">
-        <v>516.6661034235625</v>
+        <v>491.3163296063373</v>
       </c>
       <c r="I19" t="n">
-        <v>618.0089823596454</v>
+        <v>592.6592085424202</v>
       </c>
       <c r="J19" t="n">
-        <v>859.3027230120967</v>
+        <v>833.9529491948715</v>
       </c>
       <c r="K19" t="n">
-        <v>859.3027230120967</v>
+        <v>824.3360059613937</v>
       </c>
       <c r="L19" t="n">
-        <v>859.3027230120967</v>
+        <v>678.3283007515157</v>
       </c>
       <c r="M19" t="n">
-        <v>859.3027230120967</v>
+        <v>434.2559660014653</v>
       </c>
       <c r="N19" t="n">
-        <v>859.3027230120967</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="O19" t="n">
-        <v>859.3027230120967</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="Q19" t="n">
-        <v>407.9499286428058</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="R19" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S19" t="n">
         <v>65.12</v>
@@ -5709,7 +5709,7 @@
         <v>422.5399739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>422.5399739669084</v>
+        <v>413.989112502805</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>879.6685602765009</v>
+        <v>880.1035184729978</v>
       </c>
       <c r="C20" t="n">
-        <v>707.4720165967091</v>
+        <v>707.906974793206</v>
       </c>
       <c r="D20" t="n">
-        <v>574.8062027180729</v>
+        <v>575.2411609145698</v>
       </c>
       <c r="E20" t="n">
-        <v>448.1766172565894</v>
+        <v>448.6115754530863</v>
       </c>
       <c r="F20" t="n">
-        <v>321.0153761373855</v>
+        <v>321.4503343338824</v>
       </c>
       <c r="G20" t="n">
-        <v>194.9978283727226</v>
+        <v>195.4327865692196</v>
       </c>
       <c r="H20" t="n">
         <v>65.12</v>
@@ -5743,52 +5743,52 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>456.4291130376557</v>
+        <v>423.7248049231964</v>
       </c>
       <c r="K20" t="n">
-        <v>1166.135479385524</v>
+        <v>1133.431171271065</v>
       </c>
       <c r="L20" t="n">
-        <v>1693.331756443634</v>
+        <v>1939.291171271065</v>
       </c>
       <c r="M20" t="n">
-        <v>2204.180585172569</v>
+        <v>2450.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2817.400904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="O20" t="n">
-        <v>2817.400904947332</v>
+        <v>2450.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2817.400904947332</v>
+        <v>3256</v>
       </c>
       <c r="Q20" t="n">
         <v>3256</v>
       </c>
       <c r="R20" t="n">
-        <v>3256.000000000055</v>
+        <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3037.971547674476</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.188131787037</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.22722618238</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V20" t="n">
-        <v>1998.832252276497</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W20" t="n">
-        <v>1635.828741184631</v>
+        <v>1636.263699381128</v>
       </c>
       <c r="X20" t="n">
-        <v>1319.382444759714</v>
+        <v>1319.817402956211</v>
       </c>
       <c r="Y20" t="n">
-        <v>1084.718371342738</v>
+        <v>1085.153329539235</v>
       </c>
     </row>
     <row r="21">
@@ -5831,13 +5831,13 @@
         <v>710.8746758324473</v>
       </c>
       <c r="M21" t="n">
-        <v>796.9552175753066</v>
+        <v>951.0691019397386</v>
       </c>
       <c r="N21" t="n">
-        <v>930.2355021828749</v>
+        <v>1084.349386547307</v>
       </c>
       <c r="O21" t="n">
-        <v>1445.487953866594</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5919,10 +5919,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>446.72908934717</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.72908934717</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>879.6685602764463</v>
+        <v>879.6685602765154</v>
       </c>
       <c r="C23" t="n">
-        <v>707.4720165966545</v>
+        <v>707.4720165967236</v>
       </c>
       <c r="D23" t="n">
-        <v>574.8062027180183</v>
+        <v>574.8062027180874</v>
       </c>
       <c r="E23" t="n">
-        <v>448.1766172565348</v>
+        <v>448.1766172566039</v>
       </c>
       <c r="F23" t="n">
-        <v>321.0153761373309</v>
+        <v>321.0153761374</v>
       </c>
       <c r="G23" t="n">
-        <v>195.4327865692196</v>
+        <v>194.9978283727372</v>
       </c>
       <c r="H23" t="n">
         <v>65.12</v>
@@ -5980,22 +5980,22 @@
         <v>65.12</v>
       </c>
       <c r="J23" t="n">
-        <v>177.7653900957659</v>
+        <v>456.4291130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>887.4717564436343</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="L23" t="n">
-        <v>1693.331756443634</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2204.180585172569</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="N23" t="n">
-        <v>2817.400904947332</v>
+        <v>1779.355799160287</v>
       </c>
       <c r="O23" t="n">
-        <v>2817.400904947332</v>
+        <v>2011.540904947332</v>
       </c>
       <c r="P23" t="n">
         <v>2817.400904947332</v>
@@ -6004,28 +6004,28 @@
         <v>3256</v>
       </c>
       <c r="R23" t="n">
-        <v>3256</v>
+        <v>3256.000000000069</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3037.97154767449</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.188131787052</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.227226182395</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276443</v>
+        <v>1998.832252276512</v>
       </c>
       <c r="W23" t="n">
-        <v>1635.828741184576</v>
+        <v>1635.828741184645</v>
       </c>
       <c r="X23" t="n">
-        <v>1319.382444759659</v>
+        <v>1319.382444759729</v>
       </c>
       <c r="Y23" t="n">
-        <v>1084.718371342683</v>
+        <v>1084.718371342752</v>
       </c>
     </row>
     <row r="24">
@@ -6068,10 +6068,10 @@
         <v>710.8746758324473</v>
       </c>
       <c r="M24" t="n">
-        <v>796.9552175753066</v>
+        <v>1073.165217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>930.2355021828749</v>
+        <v>1206.445502182875</v>
       </c>
       <c r="O24" t="n">
         <v>1445.487953866594</v>
@@ -6144,22 +6144,22 @@
         <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>713.2950178022188</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="M25" t="n">
-        <v>469.2226830521684</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="N25" t="n">
-        <v>174.0862433837998</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="O25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P25" t="n">
-        <v>65.12</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>517.2433615971223</v>
       </c>
       <c r="R25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>253.1649250963515</v>
+        <v>796.1792075135407</v>
       </c>
       <c r="C26" t="n">
-        <v>61.84</v>
+        <v>796.1792075135407</v>
       </c>
       <c r="D26" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="E26" t="n">
-        <v>61.84</v>
+        <v>608.9679390894501</v>
       </c>
       <c r="F26" t="n">
-        <v>61.84</v>
+        <v>427.2612434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>61.84</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6223,13 +6223,13 @@
         <v>453.1491130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>453.1491130376558</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>509.6405851725166</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="N26" t="n">
-        <v>1122.86090494728</v>
+        <v>1831.639432812419</v>
       </c>
       <c r="O26" t="n">
         <v>1888.130904947306</v>
@@ -6262,7 +6262,7 @@
         <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>512.760190708043</v>
+        <v>801.9697186704736</v>
       </c>
     </row>
     <row r="27">
@@ -6296,7 +6296,7 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>416.3413981428639</v>
+        <v>212.5171006891147</v>
       </c>
       <c r="K27" t="n">
         <v>624.4599167834981</v>
@@ -6393,10 +6393,10 @@
         <v>406.0589893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="R28" t="n">
         <v>61.84</v>
@@ -6430,19 +6430,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>525.7388319673844</v>
+        <v>660.6515077640113</v>
       </c>
       <c r="C29" t="n">
-        <v>298.996833742138</v>
+        <v>433.9095095387649</v>
       </c>
       <c r="D29" t="n">
-        <v>298.996833742138</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="E29" t="n">
-        <v>298.996833742138</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="F29" t="n">
-        <v>298.996833742138</v>
+        <v>246.6982411146742</v>
       </c>
       <c r="G29" t="n">
         <v>246.6982411146742</v>
@@ -6472,7 +6472,7 @@
         <v>2342.488261541388</v>
       </c>
       <c r="P29" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q29" t="n">
         <v>3092</v>
@@ -6481,25 +6481,25 @@
         <v>3065.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3065.860001183541</v>
+        <v>2793.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>2700.531130750648</v>
+        <v>2427.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2272.024770600536</v>
+        <v>2406.937446397163</v>
       </c>
       <c r="V29" t="n">
-        <v>1863.084342149199</v>
+        <v>1997.997017945826</v>
       </c>
       <c r="W29" t="n">
-        <v>1445.535376511878</v>
+        <v>1580.448052308505</v>
       </c>
       <c r="X29" t="n">
-        <v>1074.543625541507</v>
+        <v>1209.456301338133</v>
       </c>
       <c r="Y29" t="n">
-        <v>785.3340975790759</v>
+        <v>920.2467733757028</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>61.84</v>
       </c>
       <c r="I30" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>263.9186282495398</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>675.8614443439233</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L30" t="n">
-        <v>1169.961905939123</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M30" t="n">
-        <v>1478.792447681983</v>
+        <v>1427.390920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>1834.822732289551</v>
+        <v>1783.421204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2296.61518397327</v>
+        <v>2245.213656412845</v>
       </c>
       <c r="P30" t="n">
-        <v>2631.894528442776</v>
+        <v>2580.493000882351</v>
       </c>
       <c r="Q30" t="n">
         <v>2631.894528442776</v>
@@ -6588,52 +6588,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H31" t="n">
-        <v>175.5382646830375</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I31" t="n">
-        <v>223.4211436191204</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L31" t="n">
-        <v>411.2548842715717</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M31" t="n">
-        <v>411.2548842715717</v>
+        <v>107.4412000868463</v>
       </c>
       <c r="N31" t="n">
-        <v>411.2548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="O31" t="n">
-        <v>411.2548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="P31" t="n">
-        <v>411.2548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>411.2548842715717</v>
+        <v>61.84</v>
       </c>
       <c r="R31" t="n">
         <v>61.84</v>
@@ -6651,13 +6651,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6697,16 +6697,16 @@
         <v>1154.134391781985</v>
       </c>
       <c r="L32" t="n">
-        <v>1139.518787894795</v>
+        <v>1139.5187878948</v>
       </c>
       <c r="M32" t="n">
-        <v>1645.201836286728</v>
+        <v>1123.980707086718</v>
       </c>
       <c r="N32" t="n">
-        <v>1629.663755478646</v>
+        <v>1734.113802459396</v>
       </c>
       <c r="O32" t="n">
-        <v>2394.933755478687</v>
+        <v>2499.383802459437</v>
       </c>
       <c r="P32" t="n">
         <v>3092</v>
@@ -6715,7 +6715,7 @@
         <v>3092</v>
       </c>
       <c r="R32" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S32" t="n">
         <v>2877.550748295214</v>
@@ -6767,28 +6767,28 @@
         <v>61.84</v>
       </c>
       <c r="I33" t="n">
-        <v>71.63058051381552</v>
+        <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>195.5871006891145</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>384.7799167834979</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>656.130378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M33" t="n">
-        <v>742.2109201215573</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N33" t="n">
-        <v>875.4912047291256</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O33" t="n">
-        <v>1114.533656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P33" t="n">
-        <v>1515.153000882351</v>
+        <v>1578.497298336101</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6831,46 +6831,46 @@
         <v>504.0986181306686</v>
       </c>
       <c r="D34" t="n">
-        <v>509.5077622556924</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E34" t="n">
-        <v>519.4266664671054</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F34" t="n">
-        <v>535.8776390590409</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G34" t="n">
-        <v>581.3742049459262</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H34" t="n">
-        <v>642.9807901053238</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I34" t="n">
-        <v>756.2036690414067</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J34" t="n">
-        <v>1009.377409693858</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="N34" t="n">
-        <v>1011.831843630726</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>901.5240037917935</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="P34" t="n">
-        <v>501.0715822480788</v>
+        <v>941.0737317239891</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.84</v>
+        <v>501.8421494759102</v>
       </c>
       <c r="R34" t="n">
         <v>61.84</v>
@@ -6931,19 +6931,19 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>1155.05686870288</v>
+        <v>810.0236653847477</v>
       </c>
       <c r="L35" t="n">
-        <v>1139.5187878948</v>
+        <v>794.4855845766667</v>
       </c>
       <c r="M35" t="n">
-        <v>1300.168632968601</v>
+        <v>1300.1686329686</v>
       </c>
       <c r="N35" t="n">
         <v>1910.301728341279</v>
       </c>
       <c r="O35" t="n">
-        <v>1894.763647533197</v>
+        <v>2675.571728341327</v>
       </c>
       <c r="P35" t="n">
         <v>2660.033647533245</v>
@@ -7013,19 +7013,19 @@
         <v>448.1242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N36" t="n">
-        <v>1163.581204729126</v>
+        <v>938.8355021828751</v>
       </c>
       <c r="O36" t="n">
-        <v>1402.623656412844</v>
+        <v>1177.877953866594</v>
       </c>
       <c r="P36" t="n">
-        <v>1515.153000882351</v>
+        <v>1578.497298336101</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7065,52 +7065,52 @@
         <v>486.0066123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>504.0986181306686</v>
+        <v>504.0986181306923</v>
       </c>
       <c r="D37" t="n">
-        <v>509.5077622556687</v>
+        <v>509.5077622556924</v>
       </c>
       <c r="E37" t="n">
-        <v>519.4266664670818</v>
+        <v>519.4266664671054</v>
       </c>
       <c r="F37" t="n">
-        <v>535.8776390590173</v>
+        <v>535.8776390590409</v>
       </c>
       <c r="G37" t="n">
-        <v>581.3742049459025</v>
+        <v>581.3742049459262</v>
       </c>
       <c r="H37" t="n">
-        <v>642.9807901053001</v>
+        <v>642.9807901053238</v>
       </c>
       <c r="I37" t="n">
-        <v>756.203669041383</v>
+        <v>756.2036690414067</v>
       </c>
       <c r="J37" t="n">
-        <v>1009.377409693834</v>
+        <v>1009.377409693858</v>
       </c>
       <c r="K37" t="n">
-        <v>1011.831843630703</v>
+        <v>1011.831843630726</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630703</v>
+        <v>877.9453505420606</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279132224</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630703</v>
+        <v>362.9790003660659</v>
       </c>
       <c r="O37" t="n">
-        <v>902.2945710196249</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="P37" t="n">
-        <v>501.8421494759102</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="Q37" t="n">
-        <v>501.8421494759102</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R37" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>804.0962457457251</v>
+        <v>812.6382572461436</v>
       </c>
       <c r="C38" t="n">
-        <v>644.0209141871454</v>
+        <v>652.5629256875638</v>
       </c>
       <c r="D38" t="n">
-        <v>523.4763124297214</v>
+        <v>532.0183239301398</v>
       </c>
       <c r="E38" t="n">
-        <v>408.96793908945</v>
+        <v>417.5099505898684</v>
       </c>
       <c r="F38" t="n">
-        <v>293.9279100914582</v>
+        <v>302.4699215918766</v>
       </c>
       <c r="G38" t="n">
-        <v>180.0315744480075</v>
+        <v>188.5735859484259</v>
       </c>
       <c r="H38" t="n">
         <v>61.84</v>
@@ -7165,52 +7165,52 @@
         <v>61.84</v>
       </c>
       <c r="J38" t="n">
-        <v>61.84</v>
+        <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>77.37808080808094</v>
+        <v>430.0181114556214</v>
       </c>
       <c r="L38" t="n">
-        <v>61.84</v>
+        <v>415.4025075684313</v>
       </c>
       <c r="M38" t="n">
-        <v>567.5230483919336</v>
+        <v>921.0855559603648</v>
       </c>
       <c r="N38" t="n">
-        <v>1177.656143764612</v>
+        <v>1531.218651333043</v>
       </c>
       <c r="O38" t="n">
-        <v>1942.926143764667</v>
+        <v>1894.763647533191</v>
       </c>
       <c r="P38" t="n">
-        <v>2708.196143764722</v>
+        <v>2660.033647533246</v>
       </c>
       <c r="Q38" t="n">
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3083.457988499581</v>
+        <v>3092</v>
       </c>
       <c r="S38" t="n">
-        <v>2877.550748295214</v>
+        <v>2886.092759795633</v>
       </c>
       <c r="T38" t="n">
-        <v>2578.888544528988</v>
+        <v>2587.430556029407</v>
       </c>
       <c r="U38" t="n">
-        <v>2217.048851045543</v>
+        <v>2225.590862545962</v>
       </c>
       <c r="V38" t="n">
-        <v>1874.775089260873</v>
+        <v>1883.317100761291</v>
       </c>
       <c r="W38" t="n">
-        <v>1523.892790290219</v>
+        <v>1532.434801790637</v>
       </c>
       <c r="X38" t="n">
-        <v>1219.567705986514</v>
+        <v>1228.109717486932</v>
       </c>
       <c r="Y38" t="n">
-        <v>997.0248446907499</v>
+        <v>1005.566856191168</v>
       </c>
     </row>
     <row r="39">
@@ -7244,22 +7244,22 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>258.9313981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K39" t="n">
-        <v>448.1242142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L39" t="n">
-        <v>719.4746758324475</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M39" t="n">
-        <v>805.5552175753068</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N39" t="n">
-        <v>938.8355021828751</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O39" t="n">
-        <v>1177.877953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P39" t="n">
         <v>1515.153000882351</v>
@@ -7329,22 +7329,22 @@
         <v>1011.83184363073</v>
       </c>
       <c r="L40" t="n">
-        <v>1011.83184363073</v>
+        <v>877.9453505420643</v>
       </c>
       <c r="M40" t="n">
-        <v>1011.83184363073</v>
+        <v>645.994227913226</v>
       </c>
       <c r="N40" t="n">
-        <v>1011.83184363073</v>
+        <v>362.9790003660696</v>
       </c>
       <c r="O40" t="n">
-        <v>1011.83184363073</v>
+        <v>61.84</v>
       </c>
       <c r="P40" t="n">
-        <v>941.0737317239891</v>
+        <v>61.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>501.8421494759102</v>
+        <v>61.84</v>
       </c>
       <c r="R40" t="n">
         <v>61.84</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>144.0740160054425</v>
+        <v>845.4606714968789</v>
       </c>
       <c r="C41" t="n">
-        <v>61.84</v>
+        <v>845.4606714968789</v>
       </c>
       <c r="D41" t="n">
-        <v>61.84</v>
+        <v>646.1281909515761</v>
       </c>
       <c r="E41" t="n">
-        <v>61.84</v>
+        <v>452.831938823426</v>
       </c>
       <c r="F41" t="n">
-        <v>61.84</v>
+        <v>259.0040310375554</v>
       </c>
       <c r="G41" t="n">
-        <v>61.84</v>
+        <v>258.8194532358863</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7402,25 +7402,25 @@
         <v>61.84</v>
       </c>
       <c r="J41" t="n">
-        <v>61.84</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>771.5463663478683</v>
+        <v>453.1491130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>1536.816366347868</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>2047.665195076803</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="N41" t="n">
-        <v>2660.885514851566</v>
+        <v>1218.419113037656</v>
       </c>
       <c r="O41" t="n">
-        <v>2660.885514851566</v>
+        <v>1888.13090494727</v>
       </c>
       <c r="P41" t="n">
-        <v>2660.885514851566</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="Q41" t="n">
         <v>3092</v>
@@ -7441,13 +7441,13 @@
         <v>1529.904374672105</v>
       </c>
       <c r="W41" t="n">
-        <v>1100.234196913573</v>
+        <v>1529.904374672105</v>
       </c>
       <c r="X41" t="n">
-        <v>717.1212338219889</v>
+        <v>1146.791411580522</v>
       </c>
       <c r="Y41" t="n">
-        <v>415.7904937383461</v>
+        <v>845.4606714968789</v>
       </c>
     </row>
     <row r="42">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>149.0714775021605</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="C43" t="n">
-        <v>149.0714775021605</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="D43" t="n">
-        <v>146.4380110490658</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="E43" t="n">
-        <v>77.77043040567538</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="F43" t="n">
-        <v>77.77043040567538</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="G43" t="n">
-        <v>77.77043040567538</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="H43" t="n">
+        <v>93.82287350664188</v>
+      </c>
+      <c r="I43" t="n">
+        <v>93.82287350664188</v>
+      </c>
+      <c r="J43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="K43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="L43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="M43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="N43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="O43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="P43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="R43" t="n">
+        <v>208.0034716793924</v>
+      </c>
+      <c r="S43" t="n">
         <v>61.84</v>
       </c>
-      <c r="I43" t="n">
+      <c r="T43" t="n">
         <v>61.84</v>
       </c>
-      <c r="J43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="K43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="L43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="M43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="N43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="O43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="P43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="R43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="S43" t="n">
-        <v>237.4417908110376</v>
-      </c>
-      <c r="T43" t="n">
-        <v>237.4417908110376</v>
-      </c>
       <c r="U43" t="n">
-        <v>237.4417908110376</v>
+        <v>123.2611926382866</v>
       </c>
       <c r="V43" t="n">
-        <v>237.4417908110376</v>
+        <v>123.2611926382866</v>
       </c>
       <c r="W43" t="n">
-        <v>223.9339020850682</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="X43" t="n">
-        <v>223.9339020850682</v>
+        <v>109.7533039123173</v>
       </c>
       <c r="Y43" t="n">
-        <v>223.9339020850682</v>
+        <v>109.7533039123173</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="C44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="D44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="E44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="F44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="G44" t="n">
-        <v>61.84</v>
+        <v>205.6894836373359</v>
       </c>
       <c r="H44" t="n">
         <v>61.84</v>
@@ -7648,16 +7648,16 @@
         <v>453.1491130376558</v>
       </c>
       <c r="M44" t="n">
-        <v>509.6405851724156</v>
+        <v>963.9979417665908</v>
       </c>
       <c r="N44" t="n">
-        <v>1122.860904947179</v>
+        <v>1577.218261541354</v>
       </c>
       <c r="O44" t="n">
-        <v>1888.130904947256</v>
+        <v>2342.488261541431</v>
       </c>
       <c r="P44" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q44" t="n">
         <v>3092</v>
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>866.3271322809151</v>
+        <v>550.3276895328881</v>
       </c>
       <c r="C45" t="n">
-        <v>690.4686348611986</v>
+        <v>550.3276895328881</v>
       </c>
       <c r="D45" t="n">
-        <v>690.4686348611986</v>
+        <v>550.3276895328881</v>
       </c>
       <c r="E45" t="n">
-        <v>533.2240922128019</v>
+        <v>393.0831468844915</v>
       </c>
       <c r="F45" t="n">
-        <v>379.04606964929</v>
+        <v>238.9051243209795</v>
       </c>
       <c r="G45" t="n">
         <v>238.9051243209795</v>
@@ -7721,49 +7721,49 @@
         <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>592.7215462210947</v>
+        <v>745.2493362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>1049.202007816295</v>
+        <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1320.412549559154</v>
+        <v>1472.940339607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1638.822834166722</v>
+        <v>1791.35062421531</v>
       </c>
       <c r="O45" t="n">
-        <v>2062.995285850441</v>
+        <v>2033.990324352883</v>
       </c>
       <c r="P45" t="n">
-        <v>2360.654630319948</v>
+        <v>2331.64966882239</v>
       </c>
       <c r="Q45" t="n">
-        <v>2360.654630319948</v>
+        <v>2345.431196382815</v>
       </c>
       <c r="R45" t="n">
-        <v>2249.218130488538</v>
+        <v>1981.518269824856</v>
       </c>
       <c r="S45" t="n">
-        <v>1966.830251736405</v>
+        <v>1699.130391072723</v>
       </c>
       <c r="T45" t="n">
-        <v>1746.266852526795</v>
+        <v>1478.566991863113</v>
       </c>
       <c r="U45" t="n">
-        <v>1530.902852769031</v>
+        <v>1263.202992105349</v>
       </c>
       <c r="V45" t="n">
-        <v>1301.094098030121</v>
+        <v>1033.39423736644</v>
       </c>
       <c r="W45" t="n">
-        <v>1301.094098030121</v>
+        <v>785.5425778615624</v>
       </c>
       <c r="X45" t="n">
-        <v>1065.879209701447</v>
+        <v>550.3276895328881</v>
       </c>
       <c r="Y45" t="n">
-        <v>1065.879209701447</v>
+        <v>550.3276895328881</v>
       </c>
     </row>
     <row r="46">
@@ -7794,40 +7794,40 @@
         <v>61.84</v>
       </c>
       <c r="I46" t="n">
-        <v>72.10287893608292</v>
+        <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="K46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="L46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="M46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="N46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="O46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="P46" t="n">
-        <v>143.672759546362</v>
+        <v>206.2486854735834</v>
       </c>
       <c r="Q46" t="n">
-        <v>143.672759546362</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="R46" t="n">
-        <v>143.672759546362</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="S46" t="n">
-        <v>143.672759546362</v>
+        <v>179.3539521846487</v>
       </c>
       <c r="T46" t="n">
-        <v>120.4156216612533</v>
+        <v>156.0968142995399</v>
       </c>
       <c r="U46" t="n">
         <v>156.0968142995399</v>
@@ -7973,19 +7973,19 @@
         <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>836.1353457002648</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>814.2870600406815</v>
+        <v>484.7439535754935</v>
       </c>
       <c r="Q2" t="n">
-        <v>189.0212843274853</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>16.19860000000012</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>783.5089208786653</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>884.2478695740924</v>
@@ -8222,7 +8222,7 @@
         <v>814.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>470.97656641947</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,10 +8441,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>500.8454983898731</v>
       </c>
       <c r="L8" t="n">
-        <v>113.6762873319884</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8456,10 +8456,10 @@
         <v>884.2478695740924</v>
       </c>
       <c r="P8" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406860149</v>
       </c>
       <c r="Q8" t="n">
-        <v>189.0212843274674</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8681,16 +8681,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>408.1838259709342</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8921,10 +8921,10 @@
         <v>814</v>
       </c>
       <c r="M14" t="n">
-        <v>1060.271045550332</v>
+        <v>778.7925375282217</v>
       </c>
       <c r="N14" t="n">
-        <v>815.1849144666769</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>70.24786957409245</v>
@@ -9152,10 +9152,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>884.2478695740924</v>
+        <v>231.79875049407</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>397.2700819250867</v>
       </c>
       <c r="K20" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>148.8262285640457</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>304.7782794599964</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>814.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9866,16 +9866,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>601.3242207078333</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>843.247869574119</v>
+        <v>127.3099626396352</v>
       </c>
       <c r="P26" t="n">
         <v>773.2870600407081</v>
@@ -10115,10 +10115,10 @@
         <v>843.2478695741263</v>
       </c>
       <c r="P29" t="n">
-        <v>314.3402351982015</v>
+        <v>757.3696241402899</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10343,16 +10343,16 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N32" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
         <v>843.2478695741336</v>
       </c>
       <c r="P32" t="n">
-        <v>705.7653421167823</v>
+        <v>602.3597956058396</v>
       </c>
       <c r="Q32" t="n">
         <v>188.2053843274865</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>375.2922462381532</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>718.6881742653813</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>70.24786957409245</v>
+        <v>843.2478695741409</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407299</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>50.42570624509142</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>29.85214784831823</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10823,13 +10823,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>843.2478695741481</v>
+        <v>445.5401158122395</v>
       </c>
       <c r="P38" t="n">
         <v>773.2870600407372</v>
       </c>
       <c r="Q38" t="n">
-        <v>568.171202000412</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>772.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>746.7244270585516</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2870600406814136</v>
+        <v>773.2870600407444</v>
       </c>
       <c r="Q41" t="n">
-        <v>608.2918612450952</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>601.3242207077313</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
@@ -11300,10 +11300,10 @@
         <v>843.24786957417</v>
       </c>
       <c r="P44" t="n">
-        <v>773.287060040759</v>
+        <v>757.3696241402464</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22700,16 +22700,16 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>5.662449696444128</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>29.21007785422154</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -22937,10 +22937,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>5.662449696445464</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>29.21007785422375</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>5.662449696447723</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>29.21007785422552</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,22 +23226,22 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.47319342535434</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>61.28925813745595</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23271,13 +23271,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23289,7 +23289,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R13" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23460,7 +23460,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -23469,10 +23469,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>85.78360761955734</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>153.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>8.673923371994846</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23654,16 +23654,16 @@
         <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>181.0500921949918</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>436.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>382.7066165981674</v>
       </c>
       <c r="R16" t="n">
         <v>475.6021279811511</v>
@@ -23855,16 +23855,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -23882,16 +23882,16 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>144.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>241.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>292.1850752716849</v>
+        <v>10.11394863308971</v>
       </c>
       <c r="O19" t="n">
         <v>361.445564079015</v>
@@ -23900,13 +23900,13 @@
         <v>408.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>108.2004986247733</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23924,7 +23924,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>8.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.430608614531991</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24134,13 +24134,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>69.8091295274528</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24186,10 +24186,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4306086145860206</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.4306086145176096</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24359,25 +24359,25 @@
         <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>253.5689831290532</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>446.839266425598</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>83.37347970285543</v>
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>251.266706910211</v>
       </c>
       <c r="C26" t="n">
-        <v>35.06290239760591</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24608,13 +24608,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24651,7 +24651,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>179.3632896068686</v>
@@ -24660,7 +24660,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G29" t="n">
-        <v>126.981765585827</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24696,13 +24696,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>403.4117168409833</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24821,7 +24821,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -24836,10 +24836,10 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>301.0398871857071</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>155.6813925522951</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24866,7 +24866,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>22.44364543010755</v>
@@ -25079,16 +25079,16 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>240.2408026384713</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>326.3973665406309</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>71.37347970285543</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>241.0036641940478</v>
+        <v>122.6914334194651</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25544,25 +25544,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>349.445564079015</v>
+        <v>51.3179537166061</v>
       </c>
       <c r="P40" t="n">
-        <v>326.3973665406039</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>71.37347970285543</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>155.0629023976059</v>
+        <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>197.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>190.7573722870162</v>
+        <v>190.5746402633638</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25656,7 +25656,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25751,16 +25751,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>74.11380033707866</v>
       </c>
       <c r="C43" t="n">
         <v>59.72524664804467</v>
       </c>
       <c r="D43" t="n">
-        <v>69.9290862669918</v>
+        <v>72.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>67.98090483695654</v>
       </c>
       <c r="F43" t="n">
         <v>61.38285596774193</v>
@@ -25802,7 +25802,7 @@
         <v>513.6021279811511</v>
       </c>
       <c r="S43" t="n">
-        <v>149.3734797028554</v>
+        <v>4.671642740256999</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>152.588324154612</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>262.4745782429939</v>
@@ -25848,7 +25848,7 @@
         <v>216.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>221.0096587035274</v>
+        <v>78.59866990256492</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25909,10 +25909,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
         <v>160.9376868977026</v>
@@ -25924,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>138.7395358750273</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -25957,7 +25957,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>249.951662459283</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26033,7 +26033,7 @@
         <v>500.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>538.839266425598</v>
+        <v>512.2134804695526</v>
       </c>
       <c r="R46" t="n">
         <v>539.6021279811511</v>
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4489087.984212774</v>
+        <v>4489087.984212775</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5220581.579760857</v>
+        <v>5220581.579760856</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5952075.175308939</v>
+        <v>5952075.175308942</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6617185.790812486</v>
+        <v>6617185.790812489</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7285203.977225124</v>
+        <v>7285203.977225127</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>8021917.030745508</v>
+        <v>8021917.03074551</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8757533.292502843</v>
+        <v>8757533.292502845</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>9493149.554260179</v>
+        <v>9493149.554260181</v>
       </c>
     </row>
     <row r="15">
@@ -26287,10 +26287,10 @@
         <v>1402029.391467165</v>
       </c>
       <c r="H2" t="n">
-        <v>1402029.39146717</v>
+        <v>1402029.391467165</v>
       </c>
       <c r="I2" t="n">
-        <v>1402029.391467165</v>
+        <v>1402029.391467172</v>
       </c>
       <c r="J2" t="n">
         <v>1280368.19062423</v>
@@ -26299,7 +26299,7 @@
         <v>1280368.19062423</v>
       </c>
       <c r="L2" t="n">
-        <v>1409931.16836822</v>
+        <v>1409931.168368219</v>
       </c>
       <c r="M2" t="n">
         <v>1409931.16836822</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.196455833</v>
+        <v>551386.5909530219</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165735</v>
+        <v>549634.6822137623</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037627</v>
+        <v>547880.3969009515</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682167</v>
+        <v>494181.5516694609</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925398</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.045852445</v>
+        <v>517298.0248536868</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.7754680158</v>
+        <v>515622.7544692632</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335262</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795845</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.9144927665</v>
+        <v>519822.4908174383</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912134</v>
+        <v>518092.3721158862</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666617</v>
+        <v>516359.7657913341</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.0841633691</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682331</v>
+        <v>393445.3182115989</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>521606.4017778743</v>
+        <v>526444.0072806855</v>
       </c>
       <c r="C6" t="n">
-        <v>809886.3105171337</v>
+        <v>814723.9160199447</v>
       </c>
       <c r="D6" t="n">
-        <v>811640.5958299446</v>
+        <v>816478.2013327559</v>
       </c>
       <c r="E6" t="n">
-        <v>571831.6944620091</v>
+        <v>576619.7154607648</v>
       </c>
       <c r="F6" t="n">
-        <v>757380.8105446672</v>
+        <v>762168.8315434231</v>
       </c>
       <c r="G6" t="n">
-        <v>782923.9596746252</v>
+        <v>787711.9806733809</v>
       </c>
       <c r="H6" t="n">
-        <v>806996.8946147253</v>
+        <v>811784.9156134782</v>
       </c>
       <c r="I6" t="n">
-        <v>808672.1649991494</v>
+        <v>813460.1859979088</v>
       </c>
       <c r="J6" t="n">
-        <v>341188.6530907037</v>
+        <v>345853.6816473381</v>
       </c>
       <c r="K6" t="n">
-        <v>730749.3947446456</v>
+        <v>735414.4233012798</v>
       </c>
       <c r="L6" t="n">
-        <v>738734.7748754539</v>
+        <v>743446.198550781</v>
       </c>
       <c r="M6" t="n">
-        <v>815664.8935770062</v>
+        <v>820376.317252334</v>
       </c>
       <c r="N6" t="n">
-        <v>817397.4999015583</v>
+        <v>822108.9235768858</v>
       </c>
       <c r="O6" t="n">
-        <v>663931.106046863</v>
+        <v>668596.1346034973</v>
       </c>
       <c r="P6" t="n">
-        <v>697770.1377559071</v>
+        <v>702435.1663125406</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>28</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
         <v>-0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>56.51176829726961</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -27484,10 +27484,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>56.51176829727007</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27524,7 +27524,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
@@ -27533,7 +27533,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>60.13691629132191</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>115.3536407070568</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,10 +27569,10 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27597,7 +27597,7 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>400</v>
+        <v>288.8338697978031</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27609,16 +27609,16 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>270.8086794388249</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27721,7 +27721,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T5" t="n">
         <v>307.3903671255644</v>
@@ -27749,7 +27749,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>32.07828453980466</v>
       </c>
       <c r="C6" t="n">
         <v>361.0999124455193</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>200.1819986780258</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>67.41254241445556</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27885,10 +27885,10 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9583912744579</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27897,7 +27897,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>295.8364148149722</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>400</v>
+        <v>56.51176829726978</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27919,13 +27919,13 @@
         <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>56.51176829727035</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27967,16 +27967,16 @@
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -27992,13 +27992,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>172.5204020740694</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>342.2743756165773</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28077,22 +28077,22 @@
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>43.64001080141399</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,25 +28116,25 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T10" t="n">
+        <v>344.0560075394545</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
-        <v>150.9583912744579</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28247,7 +28247,7 @@
         <v>225</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>19.11687125883891</v>
       </c>
       <c r="K12" t="n">
         <v>225</v>
@@ -28256,7 +28256,7 @@
         <v>225</v>
       </c>
       <c r="M12" t="n">
-        <v>19.1168712588388</v>
+        <v>225</v>
       </c>
       <c r="N12" t="n">
         <v>225</v>
@@ -28487,10 +28487,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>166.1982915220773</v>
       </c>
       <c r="L15" t="n">
-        <v>166.1982915220774</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
@@ -28499,10 +28499,10 @@
         <v>251</v>
       </c>
       <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>251</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>251</v>
@@ -28718,31 +28718,31 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>279</v>
       </c>
-      <c r="J18" t="n">
-        <v>155.6705902671031</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>279</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
-        <v>279</v>
+        <v>217.5442043757545</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.8785988283496</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>279</v>
@@ -28967,16 +28967,16 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>155.6705902671031</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
         <v>279</v>
-      </c>
-      <c r="P21" t="n">
-        <v>155.6705902671032</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>250.8785988283643</v>
       </c>
       <c r="S23" t="n">
         <v>279</v>
@@ -29204,16 +29204,16 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>155.6705902671032</v>
+        <v>155.6705902671034</v>
       </c>
       <c r="Q24" t="n">
         <v>279</v>
@@ -29432,10 +29432,10 @@
         <v>225</v>
       </c>
       <c r="J27" t="n">
+        <v>19.11687125883917</v>
+      </c>
+      <c r="K27" t="n">
         <v>225</v>
-      </c>
-      <c r="K27" t="n">
-        <v>19.11687125883918</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29666,10 +29666,10 @@
         <v>225</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>78.91122027701098</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29678,7 +29678,7 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N30" t="n">
         <v>225</v>
@@ -29690,7 +29690,7 @@
         <v>225</v>
       </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R30" t="n">
         <v>225</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>291</v>
+        <v>282.5434086145851</v>
       </c>
       <c r="T32" t="n">
         <v>291</v>
@@ -29903,7 +29903,7 @@
         <v>291</v>
       </c>
       <c r="I33" t="n">
-        <v>227.0158611578289</v>
+        <v>291</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>291</v>
       </c>
       <c r="Q33" t="n">
-        <v>291</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -29967,7 +29967,7 @@
         <v>291</v>
       </c>
       <c r="D34" t="n">
-        <v>291.0000000000239</v>
+        <v>291</v>
       </c>
       <c r="E34" t="n">
         <v>291</v>
@@ -30149,22 +30149,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>291</v>
+      </c>
+      <c r="Q36" t="n">
         <v>227.0158611578289</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>291</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30201,7 +30201,7 @@
         <v>291</v>
       </c>
       <c r="C37" t="n">
-        <v>291</v>
+        <v>291.0000000000239</v>
       </c>
       <c r="D37" t="n">
         <v>291</v>
@@ -30295,7 +30295,7 @@
         <v>291</v>
       </c>
       <c r="H38" t="n">
-        <v>291</v>
+        <v>282.5434086145858</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>242.4220074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30398,7 +30398,7 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>227.0158611578287</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>291</v>
@@ -30696,7 +30696,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>212.6444951096831</v>
+        <v>150.6028863841406</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30729,7 +30729,7 @@
         <v>210.0245665062577</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>213</v>
       </c>
       <c r="V43" t="n">
         <v>199.1703102162162</v>
@@ -30857,7 +30857,7 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>32.93152520344682</v>
+        <v>187</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30869,13 +30869,13 @@
         <v>187</v>
       </c>
       <c r="O45" t="n">
-        <v>187</v>
+        <v>3.633584296822391</v>
       </c>
       <c r="P45" t="n">
         <v>187</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>187</v>
       </c>
       <c r="R45" t="n">
         <v>187</v>
@@ -30930,10 +30930,10 @@
         <v>187</v>
       </c>
       <c r="I46" t="n">
-        <v>187</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>107.5617575331594</v>
+        <v>181.1363079001335</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -30966,7 +30966,7 @@
         <v>187</v>
       </c>
       <c r="U46" t="n">
-        <v>187</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V46" t="n">
         <v>187</v>
@@ -34883,7 +34883,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>114.4637819444445</v>
+        <v>3.297651742247581</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34895,16 +34895,16 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>94.1752238187066</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34986,7 +34986,7 @@
         <v>814</v>
       </c>
       <c r="L5" t="n">
-        <v>814.0000000000001</v>
+        <v>814</v>
       </c>
       <c r="M5" t="n">
         <v>814</v>
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35138,7 +35138,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>32.14359357854778</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35171,10 +35171,10 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35183,7 +35183,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.371061965509796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35235,7 +35235,7 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814</v>
+        <v>814.0000000000045</v>
       </c>
       <c r="Q8" t="n">
         <v>814</v>
@@ -35363,22 +35363,22 @@
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>8.371061965506222</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,25 +35402,25 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>134.0314410331968</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,16 +35460,16 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>337.9359563968417</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35533,7 +35533,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965146</v>
       </c>
       <c r="K12" t="n">
         <v>416.1038546407913</v>
@@ -35542,7 +35542,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
-        <v>106.0669134233431</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N12" t="n">
         <v>359.6265501086548</v>
@@ -35700,10 +35700,10 @@
         <v>814</v>
       </c>
       <c r="M14" t="n">
-        <v>516.0089179080152</v>
+        <v>234.5304098859044</v>
       </c>
       <c r="N14" t="n">
-        <v>337.9359563968417</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -35773,10 +35773,10 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>357.3021461628686</v>
       </c>
       <c r="L15" t="n">
-        <v>440.2896668707643</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
@@ -35785,10 +35785,10 @@
         <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>492.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q15" t="n">
         <v>77.92073490952041</v>
@@ -35931,10 +35931,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>435.3966095009885</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>814</v>
+        <v>161.5508809199775</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,10 +36004,10 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>280.8791965047788</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
         <v>191.1038546407913</v>
@@ -36016,19 +36016,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>365.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>520.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>105.9207349095204</v>
+        <v>44.46493928527492</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,31 +36165,31 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>362.2270756799964</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>532.5214919778891</v>
+        <v>814</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.512089101654111e-11</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36253,16 +36253,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>86.95004216450428</v>
+        <v>242.6206324316074</v>
       </c>
       <c r="N21" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>269.3365947817563</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36402,31 +36402,31 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>113.7832223189554</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L23" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>234.5304098859039</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.981979528761874e-11</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -36490,16 +36490,16 @@
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>365.9500421645043</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P24" t="n">
-        <v>269.3365947817563</v>
+        <v>269.3365947817566</v>
       </c>
       <c r="Q24" t="n">
         <v>105.9207349095204</v>
@@ -36645,16 +36645,16 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>57.06209306551599</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>773.0000000000266</v>
+        <v>57.06209306554275</v>
       </c>
       <c r="P26" t="n">
         <v>773.0000000000266</v>
@@ -36718,10 +36718,10 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36894,10 +36894,10 @@
         <v>773.0000000000339</v>
       </c>
       <c r="P29" t="n">
-        <v>314.0531751575201</v>
+        <v>757.0825640996085</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,10 +36952,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>204.1198265146867</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36964,7 +36964,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M30" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N30" t="n">
         <v>359.6265501086548</v>
@@ -36976,7 +36976,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37119,7 +37119,7 @@
         <v>773.0000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>727.1079320762982</v>
+        <v>727.1079320760407</v>
       </c>
       <c r="M32" t="n">
         <v>773.0000000000412</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>9.889475266480316</v>
+        <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37213,7 +37213,7 @@
         <v>404.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>117.9207349095204</v>
+        <v>53.9365960673493</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37253,7 +37253,7 @@
         <v>18.27475335195533</v>
       </c>
       <c r="D34" t="n">
-        <v>5.463781944468437</v>
+        <v>5.46378194444452</v>
       </c>
       <c r="E34" t="n">
         <v>10.01909516304346</v>
@@ -37353,10 +37353,10 @@
         <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760389</v>
+        <v>727.1079320762969</v>
       </c>
       <c r="L35" t="n">
-        <v>773.0000000000001</v>
+        <v>773</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000484</v>
@@ -37435,7 +37435,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
-        <v>501.1072365065158</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M36" t="n">
         <v>86.95004216450428</v>
@@ -37447,10 +37447,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>113.6660045146532</v>
+        <v>404.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>117.9207349095204</v>
+        <v>53.9365960673493</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37487,7 +37487,7 @@
         <v>3.886199662921342</v>
       </c>
       <c r="C37" t="n">
-        <v>18.27475335195533</v>
+        <v>18.27475335197925</v>
       </c>
       <c r="D37" t="n">
         <v>5.46378194444452</v>
@@ -37590,10 +37590,10 @@
         <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762811</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>727.1079320762842</v>
       </c>
       <c r="M38" t="n">
         <v>773.0000000000557</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37684,7 +37684,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>340.6818656724819</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
         <v>117.9207349095204</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>772.9999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>676.476557484459</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>773.000000000063</v>
       </c>
       <c r="Q41" t="n">
-        <v>435.4691769176098</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>177.3755462737753</v>
+        <v>115.3339375482328</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>62.04160872554206</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38070,7 +38070,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>57.06209306541402</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
@@ -38079,10 +38079,10 @@
         <v>773.0000000000775</v>
       </c>
       <c r="P44" t="n">
-        <v>773.0000000000775</v>
+        <v>757.0825640995648</v>
       </c>
       <c r="Q44" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>224.0353798442382</v>
+        <v>378.1038546407913</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38155,13 +38155,13 @@
         <v>321.6265501086548</v>
       </c>
       <c r="O45" t="n">
-        <v>428.4570219027464</v>
+        <v>245.0906061995688</v>
       </c>
       <c r="P45" t="n">
         <v>300.6660045146532</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>13.92073490952041</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -38216,10 +38216,10 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>10.36654437988173</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>72.29280869725164</v>
+        <v>145.8673590642257</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>36.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
